--- a/excel/aula05/Pagamentos.xlsx
+++ b/excel/aula05/Pagamentos.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suporte\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB2558C1-EB32-4356-AB86-010AEA83EEFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF7A90E-BB0E-43BF-B262-6D1F2128A192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="1" xr2:uid="{EFA3035D-C96B-427D-AECE-DFDBCF84149B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="2" xr2:uid="{EFA3035D-C96B-427D-AECE-DFDBCF84149B}"/>
   </bookViews>
   <sheets>
     <sheet name="Pagamentos" sheetId="1" r:id="rId1"/>
     <sheet name="Cargos" sheetId="2" r:id="rId2"/>
+    <sheet name="INSS" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
   <si>
     <t>Folha de Pagamentos</t>
   </si>
@@ -166,13 +167,48 @@
   </si>
   <si>
     <t>Supervisor</t>
+  </si>
+  <si>
+    <t>Horas mês</t>
+  </si>
+  <si>
+    <t>Sala hora</t>
+  </si>
+  <si>
+    <t>Teto</t>
+  </si>
+  <si>
+    <t>Deduzir</t>
+  </si>
+  <si>
+    <t>Porcentagem</t>
+  </si>
+  <si>
+    <t>Tabela de INSS 2025</t>
+  </si>
+  <si>
+    <t>Acima de</t>
+  </si>
+  <si>
+    <t>Salário Bruto</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,13 +224,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -206,15 +256,32 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -546,137 +613,799 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03622E34-FBB9-4C8B-A28E-3DF59708295C}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="2">
+        <f>VLOOKUP(B3,Cargos!$A$3:$D$13,3)</f>
+        <v>1214.4000000000001</v>
+      </c>
+      <c r="D3" s="5">
+        <f>VLOOKUP(B3,Cargos!$A$3:$D$13,4)</f>
+        <v>110</v>
+      </c>
+      <c r="E3" s="6">
+        <f>C3/D3</f>
+        <v>11.040000000000001</v>
+      </c>
+      <c r="F3">
+        <v>15</v>
+      </c>
+      <c r="G3" s="7">
+        <f>E3*F3*1.5</f>
+        <v>248.40000000000003</v>
+      </c>
+      <c r="H3" s="7">
+        <f>C3+G3</f>
+        <v>1462.8000000000002</v>
+      </c>
+      <c r="I3" s="10">
+        <f>VLOOKUP(H3,INSS!$B$3:$D$7,3)</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="J3" s="2">
+        <f>VLOOKUP(H3,INSS!$B$3:$D$7,2)</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="7"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="2">
+        <f>VLOOKUP(B4,Cargos!$A$3:$D$13,3)</f>
+        <v>2277</v>
+      </c>
+      <c r="D4" s="5">
+        <f>VLOOKUP(B4,Cargos!$A$3:$D$13,4)</f>
+        <v>220</v>
+      </c>
+      <c r="E4" s="6">
+        <f t="shared" ref="E4:E20" si="0">C4/D4</f>
+        <v>10.35</v>
+      </c>
+      <c r="F4">
+        <v>17</v>
+      </c>
+      <c r="G4" s="7">
+        <f t="shared" ref="G4:G20" si="1">E4*F4*1.5</f>
+        <v>263.92499999999995</v>
+      </c>
+      <c r="H4" s="7">
+        <f t="shared" ref="H4:H20" si="2">C4+G4</f>
+        <v>2540.9250000000002</v>
+      </c>
+      <c r="I4" s="10">
+        <f>VLOOKUP(H4,INSS!$B$3:$D$7,3)</f>
+        <v>0.09</v>
+      </c>
+      <c r="J4" s="2">
+        <f>VLOOKUP(H4,INSS!$B$3:$D$7,2)</f>
+        <v>22.77</v>
+      </c>
+      <c r="K4" s="7"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="2">
+        <f>VLOOKUP(B5,Cargos!$A$3:$D$13,3)</f>
+        <v>2277</v>
+      </c>
+      <c r="D5" s="5">
+        <f>VLOOKUP(B5,Cargos!$A$3:$D$13,4)</f>
+        <v>220</v>
+      </c>
+      <c r="E5" s="6">
+        <f>C5/D5</f>
+        <v>10.35</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5" s="7">
+        <f t="shared" si="1"/>
+        <v>77.625</v>
+      </c>
+      <c r="H5" s="7">
+        <f t="shared" si="2"/>
+        <v>2354.625</v>
+      </c>
+      <c r="I5" s="10">
+        <f>VLOOKUP(H5,INSS!$B$3:$D$7,3)</f>
+        <v>0.09</v>
+      </c>
+      <c r="J5" s="2">
+        <f>VLOOKUP(H5,INSS!$B$3:$D$7,2)</f>
+        <v>22.77</v>
+      </c>
+      <c r="K5" s="7"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="2">
+        <f>VLOOKUP(B6,Cargos!$A$3:$D$13,3)</f>
+        <v>1518</v>
+      </c>
+      <c r="D6" s="5">
+        <f>VLOOKUP(B6,Cargos!$A$3:$D$13,4)</f>
+        <v>220</v>
+      </c>
+      <c r="E6" s="6">
+        <f t="shared" si="0"/>
+        <v>6.9</v>
+      </c>
+      <c r="F6">
+        <v>30</v>
+      </c>
+      <c r="G6" s="7">
+        <f t="shared" si="1"/>
+        <v>310.5</v>
+      </c>
+      <c r="H6" s="7">
+        <f t="shared" si="2"/>
+        <v>1828.5</v>
+      </c>
+      <c r="I6" s="10">
+        <f>VLOOKUP(H6,INSS!$B$3:$D$7,3)</f>
+        <v>0.09</v>
+      </c>
+      <c r="J6" s="2">
+        <f>VLOOKUP(H6,INSS!$B$3:$D$7,2)</f>
+        <v>22.77</v>
+      </c>
+      <c r="K6" s="7"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="2">
+        <f>VLOOKUP(B7,Cargos!$A$3:$D$13,3)</f>
+        <v>10626</v>
+      </c>
+      <c r="D7" s="5">
+        <f>VLOOKUP(B7,Cargos!$A$3:$D$13,4)</f>
+        <v>220</v>
+      </c>
+      <c r="E7" s="6">
+        <f t="shared" si="0"/>
+        <v>48.3</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7" s="7">
+        <f t="shared" si="1"/>
+        <v>579.59999999999991</v>
+      </c>
+      <c r="H7" s="7">
+        <f t="shared" si="2"/>
+        <v>11205.6</v>
+      </c>
+      <c r="I7" s="10" t="str">
+        <f>VLOOKUP(H7,INSS!$B$3:$D$7,3)</f>
+        <v>Teto</v>
+      </c>
+      <c r="J7" s="2" t="str">
+        <f>VLOOKUP(H7,INSS!$B$3:$D$7,2)</f>
+        <v>Teto</v>
+      </c>
+      <c r="K7" s="7"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="2">
+        <f>VLOOKUP(B8,Cargos!$A$3:$D$13,3)</f>
+        <v>4554</v>
+      </c>
+      <c r="D8" s="5">
+        <f>VLOOKUP(B8,Cargos!$A$3:$D$13,4)</f>
+        <v>220</v>
+      </c>
+      <c r="E8" s="6">
+        <f t="shared" si="0"/>
+        <v>20.7</v>
+      </c>
+      <c r="F8">
+        <v>10</v>
+      </c>
+      <c r="G8" s="7">
+        <f t="shared" si="1"/>
+        <v>310.5</v>
+      </c>
+      <c r="H8" s="7">
+        <f t="shared" si="2"/>
+        <v>4864.5</v>
+      </c>
+      <c r="I8" s="10">
+        <f>VLOOKUP(H8,INSS!$B$3:$D$7,3)</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J8" s="2">
+        <f>VLOOKUP(H8,INSS!$B$3:$D$7,2)</f>
+        <v>190.42</v>
+      </c>
+      <c r="K8" s="7"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="2">
+        <f>VLOOKUP(B9,Cargos!$A$3:$D$13,3)</f>
+        <v>759</v>
+      </c>
+      <c r="D9" s="5">
+        <f>VLOOKUP(B9,Cargos!$A$3:$D$13,4)</f>
+        <v>180</v>
+      </c>
+      <c r="E9" s="6">
+        <f t="shared" si="0"/>
+        <v>4.2166666666666668</v>
+      </c>
+      <c r="F9">
+        <v>12</v>
+      </c>
+      <c r="G9" s="7">
+        <f t="shared" si="1"/>
+        <v>75.900000000000006</v>
+      </c>
+      <c r="H9" s="7">
+        <f t="shared" si="2"/>
+        <v>834.9</v>
+      </c>
+      <c r="I9" s="10">
+        <f>VLOOKUP(H9,INSS!$B$3:$D$7,3)</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="J9" s="2">
+        <f>VLOOKUP(H9,INSS!$B$3:$D$7,2)</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="7"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="2">
+        <f>VLOOKUP(B10,Cargos!$A$3:$D$13,3)</f>
+        <v>7590</v>
+      </c>
+      <c r="D10" s="5">
+        <f>VLOOKUP(B10,Cargos!$A$3:$D$13,4)</f>
+        <v>220</v>
+      </c>
+      <c r="E10" s="6">
+        <f t="shared" si="0"/>
+        <v>34.5</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="7">
+        <f t="shared" si="2"/>
+        <v>7590</v>
+      </c>
+      <c r="I10" s="10">
+        <f>VLOOKUP(H10,INSS!$B$3:$D$7,3)</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="J10" s="2">
+        <f>VLOOKUP(H10,INSS!$B$3:$D$7,2)</f>
+        <v>190.42</v>
+      </c>
+      <c r="K10" s="7"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2">
+        <f>VLOOKUP(B11,Cargos!$A$3:$D$13,3)</f>
+        <v>3036</v>
+      </c>
+      <c r="D11" s="5">
+        <f>VLOOKUP(B11,Cargos!$A$3:$D$13,4)</f>
+        <v>220</v>
+      </c>
+      <c r="E11" s="6">
+        <f t="shared" si="0"/>
+        <v>13.8</v>
+      </c>
+      <c r="F11">
+        <v>12</v>
+      </c>
+      <c r="G11" s="7">
+        <f t="shared" si="1"/>
+        <v>248.40000000000003</v>
+      </c>
+      <c r="H11" s="7">
+        <f t="shared" si="2"/>
+        <v>3284.4</v>
+      </c>
+      <c r="I11" s="10">
+        <f>VLOOKUP(H11,INSS!$B$3:$D$7,3)</f>
+        <v>0.12</v>
+      </c>
+      <c r="J11" s="2">
+        <f>VLOOKUP(H11,INSS!$B$3:$D$7,2)</f>
+        <v>106.8</v>
+      </c>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2">
+        <f>VLOOKUP(B12,Cargos!$A$3:$D$13,3)</f>
+        <v>2277</v>
+      </c>
+      <c r="D12" s="5">
+        <f>VLOOKUP(B12,Cargos!$A$3:$D$13,4)</f>
+        <v>220</v>
+      </c>
+      <c r="E12" s="6">
+        <f t="shared" si="0"/>
+        <v>10.35</v>
+      </c>
+      <c r="F12">
+        <v>18</v>
+      </c>
+      <c r="G12" s="7">
+        <f t="shared" si="1"/>
+        <v>279.45</v>
+      </c>
+      <c r="H12" s="7">
+        <f t="shared" si="2"/>
+        <v>2556.4499999999998</v>
+      </c>
+      <c r="I12" s="10">
+        <f>VLOOKUP(H12,INSS!$B$3:$D$7,3)</f>
+        <v>0.09</v>
+      </c>
+      <c r="J12" s="2">
+        <f>VLOOKUP(H12,INSS!$B$3:$D$7,2)</f>
+        <v>22.77</v>
+      </c>
+      <c r="K12" s="7"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="2">
+        <f>VLOOKUP(B13,Cargos!$A$3:$D$13,3)</f>
+        <v>3036</v>
+      </c>
+      <c r="D13" s="5">
+        <f>VLOOKUP(B13,Cargos!$A$3:$D$13,4)</f>
+        <v>220</v>
+      </c>
+      <c r="E13" s="6">
+        <f t="shared" si="0"/>
+        <v>13.8</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="7">
+        <f t="shared" si="2"/>
+        <v>3036</v>
+      </c>
+      <c r="I13" s="10">
+        <f>VLOOKUP(H13,INSS!$B$3:$D$7,3)</f>
+        <v>0.12</v>
+      </c>
+      <c r="J13" s="2">
+        <f>VLOOKUP(H13,INSS!$B$3:$D$7,2)</f>
+        <v>106.8</v>
+      </c>
+      <c r="K13" s="7"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="2">
+        <f>VLOOKUP(B14,Cargos!$A$3:$D$13,3)</f>
+        <v>3036</v>
+      </c>
+      <c r="D14" s="5">
+        <f>VLOOKUP(B14,Cargos!$A$3:$D$13,4)</f>
+        <v>220</v>
+      </c>
+      <c r="E14" s="6">
+        <f t="shared" si="0"/>
+        <v>13.8</v>
+      </c>
+      <c r="F14">
+        <v>28</v>
+      </c>
+      <c r="G14" s="7">
+        <f t="shared" si="1"/>
+        <v>579.6</v>
+      </c>
+      <c r="H14" s="7">
+        <f t="shared" si="2"/>
+        <v>3615.6</v>
+      </c>
+      <c r="I14" s="10">
+        <f>VLOOKUP(H14,INSS!$B$3:$D$7,3)</f>
+        <v>0.12</v>
+      </c>
+      <c r="J14" s="2">
+        <f>VLOOKUP(H14,INSS!$B$3:$D$7,2)</f>
+        <v>106.8</v>
+      </c>
+      <c r="K14" s="7"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="2">
+        <f>VLOOKUP(B15,Cargos!$A$3:$D$13,3)</f>
+        <v>3036</v>
+      </c>
+      <c r="D15" s="5">
+        <f>VLOOKUP(B15,Cargos!$A$3:$D$13,4)</f>
+        <v>220</v>
+      </c>
+      <c r="E15" s="6">
+        <f t="shared" si="0"/>
+        <v>13.8</v>
+      </c>
+      <c r="F15">
+        <v>24</v>
+      </c>
+      <c r="G15" s="7">
+        <f t="shared" si="1"/>
+        <v>496.80000000000007</v>
+      </c>
+      <c r="H15" s="7">
+        <f t="shared" si="2"/>
+        <v>3532.8</v>
+      </c>
+      <c r="I15" s="10">
+        <f>VLOOKUP(H15,INSS!$B$3:$D$7,3)</f>
+        <v>0.12</v>
+      </c>
+      <c r="J15" s="2">
+        <f>VLOOKUP(H15,INSS!$B$3:$D$7,2)</f>
+        <v>106.8</v>
+      </c>
+      <c r="K15" s="7"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="2">
+        <f>VLOOKUP(B16,Cargos!$A$3:$D$13,3)</f>
+        <v>1518</v>
+      </c>
+      <c r="D16" s="5">
+        <f>VLOOKUP(B16,Cargos!$A$3:$D$13,4)</f>
+        <v>220</v>
+      </c>
+      <c r="E16" s="6">
+        <f t="shared" si="0"/>
+        <v>6.9</v>
+      </c>
+      <c r="F16">
+        <v>30</v>
+      </c>
+      <c r="G16" s="7">
+        <f t="shared" si="1"/>
+        <v>310.5</v>
+      </c>
+      <c r="H16" s="7">
+        <f t="shared" si="2"/>
+        <v>1828.5</v>
+      </c>
+      <c r="I16" s="10">
+        <f>VLOOKUP(H16,INSS!$B$3:$D$7,3)</f>
+        <v>0.09</v>
+      </c>
+      <c r="J16" s="2">
+        <f>VLOOKUP(H16,INSS!$B$3:$D$7,2)</f>
+        <v>22.77</v>
+      </c>
+      <c r="K16" s="7"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="2">
+        <f>VLOOKUP(B17,Cargos!$A$3:$D$13,3)</f>
+        <v>1518</v>
+      </c>
+      <c r="D17" s="5">
+        <f>VLOOKUP(B17,Cargos!$A$3:$D$13,4)</f>
+        <v>220</v>
+      </c>
+      <c r="E17" s="6">
+        <f t="shared" si="0"/>
+        <v>6.9</v>
+      </c>
+      <c r="F17">
+        <v>22</v>
+      </c>
+      <c r="G17" s="7">
+        <f t="shared" si="1"/>
+        <v>227.70000000000002</v>
+      </c>
+      <c r="H17" s="7">
+        <f t="shared" si="2"/>
+        <v>1745.7</v>
+      </c>
+      <c r="I17" s="10">
+        <f>VLOOKUP(H17,INSS!$B$3:$D$7,3)</f>
+        <v>0.09</v>
+      </c>
+      <c r="J17" s="2">
+        <f>VLOOKUP(H17,INSS!$B$3:$D$7,2)</f>
+        <v>22.77</v>
+      </c>
+      <c r="K17" s="7"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="2">
+        <f>VLOOKUP(B18,Cargos!$A$3:$D$13,3)</f>
+        <v>1518</v>
+      </c>
+      <c r="D18" s="5">
+        <f>VLOOKUP(B18,Cargos!$A$3:$D$13,4)</f>
+        <v>220</v>
+      </c>
+      <c r="E18" s="6">
+        <f t="shared" si="0"/>
+        <v>6.9</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+      <c r="G18" s="7">
+        <f t="shared" si="1"/>
+        <v>51.75</v>
+      </c>
+      <c r="H18" s="7">
+        <f t="shared" si="2"/>
+        <v>1569.75</v>
+      </c>
+      <c r="I18" s="10">
+        <f>VLOOKUP(H18,INSS!$B$3:$D$7,3)</f>
+        <v>0.09</v>
+      </c>
+      <c r="J18" s="2">
+        <f>VLOOKUP(H18,INSS!$B$3:$D$7,2)</f>
+        <v>22.77</v>
+      </c>
+      <c r="K18" s="7"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="2">
+        <f>VLOOKUP(B19,Cargos!$A$3:$D$13,3)</f>
+        <v>2277</v>
+      </c>
+      <c r="D19" s="5">
+        <f>VLOOKUP(B19,Cargos!$A$3:$D$13,4)</f>
+        <v>220</v>
+      </c>
+      <c r="E19" s="6">
+        <f t="shared" si="0"/>
+        <v>10.35</v>
+      </c>
+      <c r="F19">
+        <v>6</v>
+      </c>
+      <c r="G19" s="7">
+        <f t="shared" si="1"/>
+        <v>93.149999999999991</v>
+      </c>
+      <c r="H19" s="7">
+        <f t="shared" si="2"/>
+        <v>2370.15</v>
+      </c>
+      <c r="I19" s="10">
+        <f>VLOOKUP(H19,INSS!$B$3:$D$7,3)</f>
+        <v>0.09</v>
+      </c>
+      <c r="J19" s="2">
+        <f>VLOOKUP(H19,INSS!$B$3:$D$7,2)</f>
+        <v>22.77</v>
+      </c>
+      <c r="K19" s="7"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="2">
+        <f>VLOOKUP(B20,Cargos!$A$3:$D$13,3)</f>
+        <v>2277</v>
+      </c>
+      <c r="D20" s="5">
+        <f>VLOOKUP(B20,Cargos!$A$3:$D$13,4)</f>
+        <v>220</v>
+      </c>
+      <c r="E20" s="6">
+        <f t="shared" si="0"/>
+        <v>10.35</v>
+      </c>
+      <c r="F20">
+        <v>9</v>
+      </c>
+      <c r="G20" s="7">
+        <f t="shared" si="1"/>
+        <v>139.72499999999999</v>
+      </c>
+      <c r="H20" s="7">
+        <f t="shared" si="2"/>
+        <v>2416.7249999999999</v>
+      </c>
+      <c r="I20" s="10">
+        <f>VLOOKUP(H20,INSS!$B$3:$D$7,3)</f>
+        <v>0.09</v>
+      </c>
+      <c r="J20" s="2">
+        <f>VLOOKUP(H20,INSS!$B$3:$D$7,2)</f>
+        <v>22.77</v>
+      </c>
+      <c r="K20" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Cargo" error="Inválido" promptTitle="Escolha" prompt="O cargo na lista" xr:uid="{190AE0BB-43E0-4EDF-A3C4-ADC27447EEFB}">
+          <x14:formula1>
+            <xm:f>Cargos!$A$3:$A$13</xm:f>
+          </x14:formula1>
+          <xm:sqref>B3:B20</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -686,27 +1415,34 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>28</v>
       </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>40</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>27</v>
       </c>
     </row>
@@ -717,10 +1453,14 @@
       <c r="B3">
         <v>0.8</v>
       </c>
+      <c r="C3" s="2">
+        <f>B3*$F$3</f>
+        <v>1214.4000000000001</v>
+      </c>
       <c r="D3">
         <v>110</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>1518</v>
       </c>
     </row>
@@ -731,6 +1471,10 @@
       <c r="B4">
         <v>1.5</v>
       </c>
+      <c r="C4" s="2">
+        <f t="shared" ref="C4:C13" si="0">B4*$F$3</f>
+        <v>2277</v>
+      </c>
       <c r="D4">
         <v>220</v>
       </c>
@@ -742,6 +1486,10 @@
       <c r="B5">
         <v>1.5</v>
       </c>
+      <c r="C5" s="2">
+        <f t="shared" si="0"/>
+        <v>2277</v>
+      </c>
       <c r="D5">
         <v>220</v>
       </c>
@@ -753,6 +1501,10 @@
       <c r="B6">
         <v>1</v>
       </c>
+      <c r="C6" s="2">
+        <f t="shared" si="0"/>
+        <v>1518</v>
+      </c>
       <c r="D6">
         <v>220</v>
       </c>
@@ -764,6 +1516,10 @@
       <c r="B7">
         <v>7</v>
       </c>
+      <c r="C7" s="2">
+        <f t="shared" si="0"/>
+        <v>10626</v>
+      </c>
       <c r="D7">
         <v>220</v>
       </c>
@@ -775,6 +1531,10 @@
       <c r="B8">
         <v>3</v>
       </c>
+      <c r="C8" s="2">
+        <f t="shared" si="0"/>
+        <v>4554</v>
+      </c>
       <c r="D8">
         <v>220</v>
       </c>
@@ -786,6 +1546,10 @@
       <c r="B9">
         <v>0.5</v>
       </c>
+      <c r="C9" s="2">
+        <f t="shared" si="0"/>
+        <v>759</v>
+      </c>
       <c r="D9">
         <v>180</v>
       </c>
@@ -797,6 +1561,10 @@
       <c r="B10">
         <v>5</v>
       </c>
+      <c r="C10" s="2">
+        <f t="shared" si="0"/>
+        <v>7590</v>
+      </c>
       <c r="D10">
         <v>220</v>
       </c>
@@ -808,6 +1576,10 @@
       <c r="B11">
         <v>2</v>
       </c>
+      <c r="C11" s="2">
+        <f t="shared" si="0"/>
+        <v>3036</v>
+      </c>
       <c r="D11">
         <v>220</v>
       </c>
@@ -819,6 +1591,10 @@
       <c r="B12">
         <v>1.5</v>
       </c>
+      <c r="C12" s="2">
+        <f t="shared" si="0"/>
+        <v>2277</v>
+      </c>
       <c r="D12">
         <v>220</v>
       </c>
@@ -829,6 +1605,10 @@
       </c>
       <c r="B13">
         <v>2</v>
+      </c>
+      <c r="C13" s="2">
+        <f t="shared" si="0"/>
+        <v>3036</v>
       </c>
       <c r="D13">
         <v>220</v>
@@ -838,6 +1618,125 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D12">
     <sortCondition ref="A2:A12"/>
   </sortState>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE3E2113-A20F-4752-9D6B-FCDAD72F6143}">
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="8" max="9" width="12.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="8">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1518.01</v>
+      </c>
+      <c r="C4" s="2">
+        <v>22.77</v>
+      </c>
+      <c r="D4" s="9">
+        <v>0.09</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2793.89</v>
+      </c>
+      <c r="C5" s="2">
+        <v>106.8</v>
+      </c>
+      <c r="D5" s="9">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="2">
+        <v>4190.84</v>
+      </c>
+      <c r="C6" s="2">
+        <v>190.42</v>
+      </c>
+      <c r="D6" s="9">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="2">
+        <v>8157.42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:D1"/>
+  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/excel/aula05/Pagamentos.xlsx
+++ b/excel/aula05/Pagamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suporte\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF7A90E-BB0E-43BF-B262-6D1F2128A192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA862519-3D76-4F62-996F-03E125B59DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="2" xr2:uid="{EFA3035D-C96B-427D-AECE-DFDBCF84149B}"/>
   </bookViews>

--- a/excel/aula05/Pagamentos.xlsx
+++ b/excel/aula05/Pagamentos.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suporte\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA862519-3D76-4F62-996F-03E125B59DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2045D341-27DB-43AE-B8DC-E081882AFAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" activeTab="2" xr2:uid="{EFA3035D-C96B-427D-AECE-DFDBCF84149B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{EFA3035D-C96B-427D-AECE-DFDBCF84149B}"/>
   </bookViews>
   <sheets>
     <sheet name="Pagamentos" sheetId="1" r:id="rId1"/>
     <sheet name="Cargos" sheetId="2" r:id="rId2"/>
     <sheet name="INSS" sheetId="3" r:id="rId3"/>
+    <sheet name="IRRF" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="54">
   <si>
     <t>Folha de Pagamentos</t>
   </si>
@@ -191,6 +192,15 @@
   </si>
   <si>
     <t>Salário Bruto</t>
+  </si>
+  <si>
+    <t>Salário Líquido</t>
+  </si>
+  <si>
+    <t>Tabela de IRRF 2025</t>
+  </si>
+  <si>
+    <t>De</t>
   </si>
 </sst>
 </file>
@@ -199,7 +209,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -261,22 +271,23 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -613,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03622E34-FBB9-4C8B-A28E-3DF59708295C}">
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
@@ -625,16 +636,17 @@
     <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -671,8 +683,11 @@
       <c r="L2" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -683,26 +698,26 @@
         <f>VLOOKUP(B3,Cargos!$A$3:$D$13,3)</f>
         <v>1214.4000000000001</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="3">
         <f>VLOOKUP(B3,Cargos!$A$3:$D$13,4)</f>
         <v>110</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="4">
         <f>C3/D3</f>
         <v>11.040000000000001</v>
       </c>
       <c r="F3">
         <v>15</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="5">
         <f>E3*F3*1.5</f>
         <v>248.40000000000003</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="5">
         <f>C3+G3</f>
         <v>1462.8000000000002</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="8">
         <f>VLOOKUP(H3,INSS!$B$3:$D$7,3)</f>
         <v>7.4999999999999997E-2</v>
       </c>
@@ -710,9 +725,21 @@
         <f>VLOOKUP(H3,INSS!$B$3:$D$7,2)</f>
         <v>0</v>
       </c>
-      <c r="K3" s="7"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K3" s="5">
+        <f>IF(I3&lt;&gt;"Teto",H3*I3-J3,INSS!$F$7)</f>
+        <v>109.71000000000001</v>
+      </c>
+      <c r="L3" s="5">
+        <f>H3*8%</f>
+        <v>117.02400000000002</v>
+      </c>
+      <c r="M3" s="5">
+        <f>H3-K3</f>
+        <v>1353.0900000000001</v>
+      </c>
+      <c r="O3" s="5"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -723,26 +750,26 @@
         <f>VLOOKUP(B4,Cargos!$A$3:$D$13,3)</f>
         <v>2277</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="3">
         <f>VLOOKUP(B4,Cargos!$A$3:$D$13,4)</f>
         <v>220</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <f t="shared" ref="E4:E20" si="0">C4/D4</f>
         <v>10.35</v>
       </c>
       <c r="F4">
         <v>17</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="5">
         <f t="shared" ref="G4:G20" si="1">E4*F4*1.5</f>
         <v>263.92499999999995</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="5">
         <f t="shared" ref="H4:H20" si="2">C4+G4</f>
         <v>2540.9250000000002</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="8">
         <f>VLOOKUP(H4,INSS!$B$3:$D$7,3)</f>
         <v>0.09</v>
       </c>
@@ -750,9 +777,21 @@
         <f>VLOOKUP(H4,INSS!$B$3:$D$7,2)</f>
         <v>22.77</v>
       </c>
-      <c r="K4" s="7"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K4" s="5">
+        <f>IF(I4&lt;&gt;"Teto",H4*I4-J4,INSS!$F$7)</f>
+        <v>205.91325000000001</v>
+      </c>
+      <c r="L4" s="5">
+        <f t="shared" ref="L4:L20" si="3">H4*8%</f>
+        <v>203.27400000000003</v>
+      </c>
+      <c r="M4" s="5">
+        <f t="shared" ref="M4:M20" si="4">H4-K4</f>
+        <v>2335.0117500000001</v>
+      </c>
+      <c r="O4" s="7"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -763,26 +802,26 @@
         <f>VLOOKUP(B5,Cargos!$A$3:$D$13,3)</f>
         <v>2277</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="3">
         <f>VLOOKUP(B5,Cargos!$A$3:$D$13,4)</f>
         <v>220</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <f>C5/D5</f>
         <v>10.35</v>
       </c>
       <c r="F5">
         <v>5</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="5">
         <f t="shared" si="1"/>
         <v>77.625</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="5">
         <f t="shared" si="2"/>
         <v>2354.625</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="8">
         <f>VLOOKUP(H5,INSS!$B$3:$D$7,3)</f>
         <v>0.09</v>
       </c>
@@ -790,9 +829,21 @@
         <f>VLOOKUP(H5,INSS!$B$3:$D$7,2)</f>
         <v>22.77</v>
       </c>
-      <c r="K5" s="7"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K5" s="5">
+        <f>IF(I5&lt;&gt;"Teto",H5*I5-J5,INSS!$F$7)</f>
+        <v>189.14624999999998</v>
+      </c>
+      <c r="L5" s="5">
+        <f t="shared" si="3"/>
+        <v>188.37</v>
+      </c>
+      <c r="M5" s="5">
+        <f t="shared" si="4"/>
+        <v>2165.4787500000002</v>
+      </c>
+      <c r="O5" s="5"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -803,26 +854,26 @@
         <f>VLOOKUP(B6,Cargos!$A$3:$D$13,3)</f>
         <v>1518</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="3">
         <f>VLOOKUP(B6,Cargos!$A$3:$D$13,4)</f>
         <v>220</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="4">
         <f t="shared" si="0"/>
         <v>6.9</v>
       </c>
       <c r="F6">
         <v>30</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="5">
         <f t="shared" si="1"/>
         <v>310.5</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="5">
         <f t="shared" si="2"/>
         <v>1828.5</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="8">
         <f>VLOOKUP(H6,INSS!$B$3:$D$7,3)</f>
         <v>0.09</v>
       </c>
@@ -830,9 +881,21 @@
         <f>VLOOKUP(H6,INSS!$B$3:$D$7,2)</f>
         <v>22.77</v>
       </c>
-      <c r="K6" s="7"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K6" s="5">
+        <f>IF(I6&lt;&gt;"Teto",H6*I6-J6,INSS!$F$7)</f>
+        <v>141.79499999999999</v>
+      </c>
+      <c r="L6" s="5">
+        <f t="shared" si="3"/>
+        <v>146.28</v>
+      </c>
+      <c r="M6" s="5">
+        <f t="shared" si="4"/>
+        <v>1686.7049999999999</v>
+      </c>
+      <c r="O6" s="5"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -843,26 +906,26 @@
         <f>VLOOKUP(B7,Cargos!$A$3:$D$13,3)</f>
         <v>10626</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="3">
         <f>VLOOKUP(B7,Cargos!$A$3:$D$13,4)</f>
         <v>220</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="4">
         <f t="shared" si="0"/>
         <v>48.3</v>
       </c>
       <c r="F7">
-        <v>8</v>
-      </c>
-      <c r="G7" s="7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
         <f t="shared" si="1"/>
-        <v>579.59999999999991</v>
-      </c>
-      <c r="H7" s="7">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
         <f t="shared" si="2"/>
-        <v>11205.6</v>
-      </c>
-      <c r="I7" s="10" t="str">
+        <v>10626</v>
+      </c>
+      <c r="I7" s="8" t="str">
         <f>VLOOKUP(H7,INSS!$B$3:$D$7,3)</f>
         <v>Teto</v>
       </c>
@@ -870,9 +933,20 @@
         <f>VLOOKUP(H7,INSS!$B$3:$D$7,2)</f>
         <v>Teto</v>
       </c>
-      <c r="K7" s="7"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K7" s="5">
+        <f>IF(I7&lt;&gt;"Teto",H7*I7-J7,INSS!$F$7)</f>
+        <v>951.61880000000008</v>
+      </c>
+      <c r="L7" s="5">
+        <f t="shared" si="3"/>
+        <v>850.08</v>
+      </c>
+      <c r="M7" s="5">
+        <f t="shared" si="4"/>
+        <v>9674.3811999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -883,26 +957,26 @@
         <f>VLOOKUP(B8,Cargos!$A$3:$D$13,3)</f>
         <v>4554</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="3">
         <f>VLOOKUP(B8,Cargos!$A$3:$D$13,4)</f>
         <v>220</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="4">
         <f t="shared" si="0"/>
         <v>20.7</v>
       </c>
       <c r="F8">
         <v>10</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="5">
         <f t="shared" si="1"/>
         <v>310.5</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="5">
         <f t="shared" si="2"/>
         <v>4864.5</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="8">
         <f>VLOOKUP(H8,INSS!$B$3:$D$7,3)</f>
         <v>0.14000000000000001</v>
       </c>
@@ -910,9 +984,20 @@
         <f>VLOOKUP(H8,INSS!$B$3:$D$7,2)</f>
         <v>190.42</v>
       </c>
-      <c r="K8" s="7"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K8" s="5">
+        <f>IF(I8&lt;&gt;"Teto",H8*I8-J8,INSS!$F$7)</f>
+        <v>490.61000000000013</v>
+      </c>
+      <c r="L8" s="5">
+        <f t="shared" si="3"/>
+        <v>389.16</v>
+      </c>
+      <c r="M8" s="5">
+        <f t="shared" si="4"/>
+        <v>4373.8899999999994</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -923,26 +1008,26 @@
         <f>VLOOKUP(B9,Cargos!$A$3:$D$13,3)</f>
         <v>759</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="3">
         <f>VLOOKUP(B9,Cargos!$A$3:$D$13,4)</f>
         <v>180</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="4">
         <f t="shared" si="0"/>
         <v>4.2166666666666668</v>
       </c>
       <c r="F9">
         <v>12</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="5">
         <f t="shared" si="1"/>
         <v>75.900000000000006</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="5">
         <f t="shared" si="2"/>
         <v>834.9</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="8">
         <f>VLOOKUP(H9,INSS!$B$3:$D$7,3)</f>
         <v>7.4999999999999997E-2</v>
       </c>
@@ -950,9 +1035,20 @@
         <f>VLOOKUP(H9,INSS!$B$3:$D$7,2)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="7"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K9" s="5">
+        <f>IF(I9&lt;&gt;"Teto",H9*I9-J9,INSS!$F$7)</f>
+        <v>62.617499999999993</v>
+      </c>
+      <c r="L9" s="5">
+        <f t="shared" si="3"/>
+        <v>66.792000000000002</v>
+      </c>
+      <c r="M9" s="5">
+        <f t="shared" si="4"/>
+        <v>772.28250000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -963,26 +1059,26 @@
         <f>VLOOKUP(B10,Cargos!$A$3:$D$13,3)</f>
         <v>7590</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="3">
         <f>VLOOKUP(B10,Cargos!$A$3:$D$13,4)</f>
         <v>220</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="4">
         <f t="shared" si="0"/>
         <v>34.5</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="5">
         <f t="shared" si="2"/>
         <v>7590</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="8">
         <f>VLOOKUP(H10,INSS!$B$3:$D$7,3)</f>
         <v>0.14000000000000001</v>
       </c>
@@ -990,9 +1086,20 @@
         <f>VLOOKUP(H10,INSS!$B$3:$D$7,2)</f>
         <v>190.42</v>
       </c>
-      <c r="K10" s="7"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K10" s="5">
+        <f>IF(I10&lt;&gt;"Teto",H10*I10-J10,INSS!$F$7)</f>
+        <v>872.18000000000018</v>
+      </c>
+      <c r="L10" s="5">
+        <f t="shared" si="3"/>
+        <v>607.20000000000005</v>
+      </c>
+      <c r="M10" s="5">
+        <f t="shared" si="4"/>
+        <v>6717.82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1003,26 +1110,26 @@
         <f>VLOOKUP(B11,Cargos!$A$3:$D$13,3)</f>
         <v>3036</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="3">
         <f>VLOOKUP(B11,Cargos!$A$3:$D$13,4)</f>
         <v>220</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="4">
         <f t="shared" si="0"/>
         <v>13.8</v>
       </c>
       <c r="F11">
         <v>12</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="5">
         <f t="shared" si="1"/>
         <v>248.40000000000003</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="5">
         <f t="shared" si="2"/>
         <v>3284.4</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="8">
         <f>VLOOKUP(H11,INSS!$B$3:$D$7,3)</f>
         <v>0.12</v>
       </c>
@@ -1030,9 +1137,20 @@
         <f>VLOOKUP(H11,INSS!$B$3:$D$7,2)</f>
         <v>106.8</v>
       </c>
-      <c r="K11" s="7"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K11" s="5">
+        <f>IF(I11&lt;&gt;"Teto",H11*I11-J11,INSS!$F$7)</f>
+        <v>287.32799999999997</v>
+      </c>
+      <c r="L11" s="5">
+        <f t="shared" si="3"/>
+        <v>262.75200000000001</v>
+      </c>
+      <c r="M11" s="5">
+        <f t="shared" si="4"/>
+        <v>2997.0720000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1043,26 +1161,26 @@
         <f>VLOOKUP(B12,Cargos!$A$3:$D$13,3)</f>
         <v>2277</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="3">
         <f>VLOOKUP(B12,Cargos!$A$3:$D$13,4)</f>
         <v>220</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="4">
         <f t="shared" si="0"/>
         <v>10.35</v>
       </c>
       <c r="F12">
         <v>18</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="5">
         <f t="shared" si="1"/>
         <v>279.45</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="5">
         <f t="shared" si="2"/>
         <v>2556.4499999999998</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="8">
         <f>VLOOKUP(H12,INSS!$B$3:$D$7,3)</f>
         <v>0.09</v>
       </c>
@@ -1070,9 +1188,20 @@
         <f>VLOOKUP(H12,INSS!$B$3:$D$7,2)</f>
         <v>22.77</v>
       </c>
-      <c r="K12" s="7"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K12" s="5">
+        <f>IF(I12&lt;&gt;"Teto",H12*I12-J12,INSS!$F$7)</f>
+        <v>207.31049999999996</v>
+      </c>
+      <c r="L12" s="5">
+        <f t="shared" si="3"/>
+        <v>204.51599999999999</v>
+      </c>
+      <c r="M12" s="5">
+        <f t="shared" si="4"/>
+        <v>2349.1394999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1083,26 +1212,26 @@
         <f>VLOOKUP(B13,Cargos!$A$3:$D$13,3)</f>
         <v>3036</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="3">
         <f>VLOOKUP(B13,Cargos!$A$3:$D$13,4)</f>
         <v>220</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="4">
         <f t="shared" si="0"/>
         <v>13.8</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="5">
         <f t="shared" si="2"/>
         <v>3036</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="8">
         <f>VLOOKUP(H13,INSS!$B$3:$D$7,3)</f>
         <v>0.12</v>
       </c>
@@ -1110,9 +1239,20 @@
         <f>VLOOKUP(H13,INSS!$B$3:$D$7,2)</f>
         <v>106.8</v>
       </c>
-      <c r="K13" s="7"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K13" s="5">
+        <f>IF(I13&lt;&gt;"Teto",H13*I13-J13,INSS!$F$7)</f>
+        <v>257.52</v>
+      </c>
+      <c r="L13" s="5">
+        <f t="shared" si="3"/>
+        <v>242.88</v>
+      </c>
+      <c r="M13" s="5">
+        <f t="shared" si="4"/>
+        <v>2778.48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1123,26 +1263,26 @@
         <f>VLOOKUP(B14,Cargos!$A$3:$D$13,3)</f>
         <v>3036</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="3">
         <f>VLOOKUP(B14,Cargos!$A$3:$D$13,4)</f>
         <v>220</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="4">
         <f t="shared" si="0"/>
         <v>13.8</v>
       </c>
       <c r="F14">
         <v>28</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="5">
         <f t="shared" si="1"/>
         <v>579.6</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="5">
         <f t="shared" si="2"/>
         <v>3615.6</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="8">
         <f>VLOOKUP(H14,INSS!$B$3:$D$7,3)</f>
         <v>0.12</v>
       </c>
@@ -1150,9 +1290,20 @@
         <f>VLOOKUP(H14,INSS!$B$3:$D$7,2)</f>
         <v>106.8</v>
       </c>
-      <c r="K14" s="7"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K14" s="5">
+        <f>IF(I14&lt;&gt;"Teto",H14*I14-J14,INSS!$F$7)</f>
+        <v>327.07199999999995</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="3"/>
+        <v>289.24799999999999</v>
+      </c>
+      <c r="M14" s="5">
+        <f t="shared" si="4"/>
+        <v>3288.5279999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1163,26 +1314,26 @@
         <f>VLOOKUP(B15,Cargos!$A$3:$D$13,3)</f>
         <v>3036</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="3">
         <f>VLOOKUP(B15,Cargos!$A$3:$D$13,4)</f>
         <v>220</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="4">
         <f t="shared" si="0"/>
         <v>13.8</v>
       </c>
       <c r="F15">
         <v>24</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="5">
         <f t="shared" si="1"/>
         <v>496.80000000000007</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="5">
         <f t="shared" si="2"/>
         <v>3532.8</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="8">
         <f>VLOOKUP(H15,INSS!$B$3:$D$7,3)</f>
         <v>0.12</v>
       </c>
@@ -1190,9 +1341,20 @@
         <f>VLOOKUP(H15,INSS!$B$3:$D$7,2)</f>
         <v>106.8</v>
       </c>
-      <c r="K15" s="7"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K15" s="5">
+        <f>IF(I15&lt;&gt;"Teto",H15*I15-J15,INSS!$F$7)</f>
+        <v>317.13599999999997</v>
+      </c>
+      <c r="L15" s="5">
+        <f t="shared" si="3"/>
+        <v>282.62400000000002</v>
+      </c>
+      <c r="M15" s="5">
+        <f t="shared" si="4"/>
+        <v>3215.6640000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1203,26 +1365,26 @@
         <f>VLOOKUP(B16,Cargos!$A$3:$D$13,3)</f>
         <v>1518</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="3">
         <f>VLOOKUP(B16,Cargos!$A$3:$D$13,4)</f>
         <v>220</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="4">
         <f t="shared" si="0"/>
         <v>6.9</v>
       </c>
       <c r="F16">
         <v>30</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="5">
         <f t="shared" si="1"/>
         <v>310.5</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="5">
         <f t="shared" si="2"/>
         <v>1828.5</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="8">
         <f>VLOOKUP(H16,INSS!$B$3:$D$7,3)</f>
         <v>0.09</v>
       </c>
@@ -1230,9 +1392,20 @@
         <f>VLOOKUP(H16,INSS!$B$3:$D$7,2)</f>
         <v>22.77</v>
       </c>
-      <c r="K16" s="7"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K16" s="5">
+        <f>IF(I16&lt;&gt;"Teto",H16*I16-J16,INSS!$F$7)</f>
+        <v>141.79499999999999</v>
+      </c>
+      <c r="L16" s="5">
+        <f t="shared" si="3"/>
+        <v>146.28</v>
+      </c>
+      <c r="M16" s="5">
+        <f t="shared" si="4"/>
+        <v>1686.7049999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1243,26 +1416,26 @@
         <f>VLOOKUP(B17,Cargos!$A$3:$D$13,3)</f>
         <v>1518</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="3">
         <f>VLOOKUP(B17,Cargos!$A$3:$D$13,4)</f>
         <v>220</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="4">
         <f t="shared" si="0"/>
         <v>6.9</v>
       </c>
       <c r="F17">
         <v>22</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="5">
         <f t="shared" si="1"/>
         <v>227.70000000000002</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="5">
         <f t="shared" si="2"/>
         <v>1745.7</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="8">
         <f>VLOOKUP(H17,INSS!$B$3:$D$7,3)</f>
         <v>0.09</v>
       </c>
@@ -1270,9 +1443,20 @@
         <f>VLOOKUP(H17,INSS!$B$3:$D$7,2)</f>
         <v>22.77</v>
       </c>
-      <c r="K17" s="7"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K17" s="5">
+        <f>IF(I17&lt;&gt;"Teto",H17*I17-J17,INSS!$F$7)</f>
+        <v>134.34299999999999</v>
+      </c>
+      <c r="L17" s="5">
+        <f t="shared" si="3"/>
+        <v>139.65600000000001</v>
+      </c>
+      <c r="M17" s="5">
+        <f t="shared" si="4"/>
+        <v>1611.357</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1283,26 +1467,26 @@
         <f>VLOOKUP(B18,Cargos!$A$3:$D$13,3)</f>
         <v>1518</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="3">
         <f>VLOOKUP(B18,Cargos!$A$3:$D$13,4)</f>
         <v>220</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="4">
         <f t="shared" si="0"/>
         <v>6.9</v>
       </c>
       <c r="F18">
         <v>5</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="5">
         <f t="shared" si="1"/>
         <v>51.75</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="5">
         <f t="shared" si="2"/>
         <v>1569.75</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="8">
         <f>VLOOKUP(H18,INSS!$B$3:$D$7,3)</f>
         <v>0.09</v>
       </c>
@@ -1310,9 +1494,20 @@
         <f>VLOOKUP(H18,INSS!$B$3:$D$7,2)</f>
         <v>22.77</v>
       </c>
-      <c r="K18" s="7"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K18" s="5">
+        <f>IF(I18&lt;&gt;"Teto",H18*I18-J18,INSS!$F$7)</f>
+        <v>118.50750000000001</v>
+      </c>
+      <c r="L18" s="5">
+        <f t="shared" si="3"/>
+        <v>125.58</v>
+      </c>
+      <c r="M18" s="5">
+        <f t="shared" si="4"/>
+        <v>1451.2425000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1323,26 +1518,26 @@
         <f>VLOOKUP(B19,Cargos!$A$3:$D$13,3)</f>
         <v>2277</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="3">
         <f>VLOOKUP(B19,Cargos!$A$3:$D$13,4)</f>
         <v>220</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="4">
         <f t="shared" si="0"/>
         <v>10.35</v>
       </c>
       <c r="F19">
         <v>6</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="5">
         <f t="shared" si="1"/>
         <v>93.149999999999991</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="5">
         <f t="shared" si="2"/>
         <v>2370.15</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="8">
         <f>VLOOKUP(H19,INSS!$B$3:$D$7,3)</f>
         <v>0.09</v>
       </c>
@@ -1350,9 +1545,20 @@
         <f>VLOOKUP(H19,INSS!$B$3:$D$7,2)</f>
         <v>22.77</v>
       </c>
-      <c r="K19" s="7"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K19" s="5">
+        <f>IF(I19&lt;&gt;"Teto",H19*I19-J19,INSS!$F$7)</f>
+        <v>190.54349999999999</v>
+      </c>
+      <c r="L19" s="5">
+        <f t="shared" si="3"/>
+        <v>189.61200000000002</v>
+      </c>
+      <c r="M19" s="5">
+        <f t="shared" si="4"/>
+        <v>2179.6064999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1363,26 +1569,26 @@
         <f>VLOOKUP(B20,Cargos!$A$3:$D$13,3)</f>
         <v>2277</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="3">
         <f>VLOOKUP(B20,Cargos!$A$3:$D$13,4)</f>
         <v>220</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="4">
         <f t="shared" si="0"/>
         <v>10.35</v>
       </c>
       <c r="F20">
         <v>9</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="5">
         <f t="shared" si="1"/>
         <v>139.72499999999999</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="5">
         <f t="shared" si="2"/>
         <v>2416.7249999999999</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="8">
         <f>VLOOKUP(H20,INSS!$B$3:$D$7,3)</f>
         <v>0.09</v>
       </c>
@@ -1390,7 +1596,18 @@
         <f>VLOOKUP(H20,INSS!$B$3:$D$7,2)</f>
         <v>22.77</v>
       </c>
-      <c r="K20" s="7"/>
+      <c r="K20" s="5">
+        <f>IF(I20&lt;&gt;"Teto",H20*I20-J20,INSS!$F$7)</f>
+        <v>194.73524999999998</v>
+      </c>
+      <c r="L20" s="5">
+        <f t="shared" si="3"/>
+        <v>193.33799999999999</v>
+      </c>
+      <c r="M20" s="5">
+        <f t="shared" si="4"/>
+        <v>2221.9897499999997</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1422,12 +1639,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -1638,11 +1855,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -1665,7 +1882,7 @@
       <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="6">
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
@@ -1679,11 +1896,11 @@
       <c r="C4" s="2">
         <v>22.77</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="7">
         <v>0.09</v>
       </c>
       <c r="F4" s="2"/>
-      <c r="G4" s="9"/>
+      <c r="G4" s="7"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
@@ -1697,7 +1914,7 @@
       <c r="C5" s="2">
         <v>106.8</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="7">
         <v>0.12</v>
       </c>
     </row>
@@ -1711,7 +1928,7 @@
       <c r="C6" s="2">
         <v>190.42</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="7">
         <v>0.14000000000000001</v>
       </c>
       <c r="F6" t="s">
@@ -1728,10 +1945,134 @@
       <c r="C7" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="7"/>
+      <c r="F7" s="5">
+        <f>B7*D6-C6</f>
+        <v>951.61880000000008</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{634D263C-688C-4774-B4A2-E57A21E8F14C}">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B1" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2259.21</v>
+      </c>
+      <c r="C4" s="2">
+        <v>169.44</v>
+      </c>
+      <c r="D4" s="11">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2826.66</v>
+      </c>
+      <c r="C5" s="2">
+        <v>381.44</v>
+      </c>
+      <c r="D5" s="11">
+        <v>0.15</v>
+      </c>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="2">
+        <v>3571.06</v>
+      </c>
+      <c r="C6" s="2">
+        <v>662.77</v>
+      </c>
+      <c r="D6" s="11">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="2">
+        <v>4668.68</v>
+      </c>
+      <c r="C7" s="2">
+        <v>896</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I11" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/excel/aula05/Pagamentos.xlsx
+++ b/excel/aula05/Pagamentos.xlsx
@@ -5,18 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Suporte\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Professor\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2045D341-27DB-43AE-B8DC-E081882AFAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D47F5C44-3D09-4CBF-BE32-DDB8BAA87C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{EFA3035D-C96B-427D-AECE-DFDBCF84149B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{EFA3035D-C96B-427D-AECE-DFDBCF84149B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Pagamentos" sheetId="1" r:id="rId1"/>
-    <sheet name="Cargos" sheetId="2" r:id="rId2"/>
-    <sheet name="INSS" sheetId="3" r:id="rId3"/>
-    <sheet name="IRRF" sheetId="4" r:id="rId4"/>
+    <sheet name="Horas Extras" sheetId="10" r:id="rId1"/>
+    <sheet name="Salário Base" sheetId="6" r:id="rId2"/>
+    <sheet name="Pagamentos" sheetId="1" r:id="rId3"/>
+    <sheet name="Cargos" sheetId="2" r:id="rId4"/>
+    <sheet name="INSS" sheetId="3" r:id="rId5"/>
+    <sheet name="IRRF" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="66">
   <si>
     <t>Folha de Pagamentos</t>
   </si>
@@ -201,6 +203,42 @@
   </si>
   <si>
     <t>De</t>
+  </si>
+  <si>
+    <t>IRRF%</t>
+  </si>
+  <si>
+    <t>IR Deduzir</t>
+  </si>
+  <si>
+    <t>IRRF R$</t>
+  </si>
+  <si>
+    <t>Sal. Final</t>
+  </si>
+  <si>
+    <t>Estatísticas</t>
+  </si>
+  <si>
+    <t>Total (Soma)</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Maximo</t>
+  </si>
+  <si>
+    <t>Mínimo</t>
+  </si>
+  <si>
+    <t>Total Folha</t>
+  </si>
+  <si>
+    <t>Compulsório</t>
+  </si>
+  <si>
+    <t>Horas Extras</t>
   </si>
 </sst>
 </file>
@@ -271,7 +309,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -281,13 +319,16 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -305,6 +346,2837 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Pagamentos!$F$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>H. Extras</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Pagamentos!$B$3:$B$20</c:f>
+              <c:strCache>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>Aprendiz</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Auxiliar Adm</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Auxiliar Limpeza</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Auxiliar Produção</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Diretor</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Encarregado</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Estagiário</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Gerente</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Operador de Produção</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Recepcionista</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Supervisor</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Operador de Produção</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Operador de Produção</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Auxiliar Produção</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Auxiliar Produção</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Auxiliar Produção</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Auxiliar Limpeza</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Auxiliar Adm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Pagamentos!$F$3:$F$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4C17-4944-BA23-C78678BAF8F0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="240935439"/>
+        <c:axId val="240934959"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="240935439"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="240934959"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="240934959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="240935439"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.27007580551410659"/>
+          <c:y val="0.21164783577267773"/>
+          <c:w val="0.60515580560504589"/>
+          <c:h val="0.67748757861931941"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Pagamentos!$C$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Salário Base</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Pagamentos!$B$3:$B$20</c:f>
+              <c:strCache>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>Aprendiz</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Auxiliar Adm</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Auxiliar Limpeza</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Auxiliar Produção</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Diretor</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Encarregado</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Estagiário</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Gerente</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Operador de Produção</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Recepcionista</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Supervisor</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Operador de Produção</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Operador de Produção</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Auxiliar Produção</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Auxiliar Produção</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Auxiliar Produção</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Auxiliar Limpeza</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Auxiliar Adm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Pagamentos!$C$3:$C$20</c:f>
+              <c:numCache>
+                <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>1214.4000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2277</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2277</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1518</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10626</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4554</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>759</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7590</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3036</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2277</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3036</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3036</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3036</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1518</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1518</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1518</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2277</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2277</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F060-4224-9B3C-81D5B359D276}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="247773039"/>
+        <c:axId val="247771119"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="247773039"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="500" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="247771119"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="247771119"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(&quot;R$&quot;* #,##0.00_);_(&quot;R$&quot;* \(#,##0.00\);_(&quot;R$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="247773039"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Cargos!$E$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Horas Extras</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Cargos!$A$3:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>Aprendiz</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Auxiliar Adm</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Auxiliar Limpeza</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Auxiliar Produção</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Diretor</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Encarregado</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Estagiário</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Gerente</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Operador de Produção</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Recepcionista</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Supervisor</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Cargos!$E$3:$E$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0A90-4F73-9EDB-CC08E38AD815}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="373728895"/>
+        <c:axId val="373727935"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="373728895"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="373727935"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="373727935"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="373728895"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{6B8CBE93-AE44-4DA1-B639-D01C6AD0BFC6}">
+  <sheetPr/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>57151</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D6C81A6-FD48-4F22-A55E-69CDC18F3D7A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="2639122" cy="2225598"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D72759B3-9201-B019-F396-F7FABBADAC66}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>29307</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>542192</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>36634</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EA53549-B28C-DE6A-9DC2-FBD76DE82172}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -623,30 +3495,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FC40315-C2BC-4C0D-918B-3F23DD52307D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03622E34-FBB9-4C8B-A28E-3DF59708295C}">
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -686,8 +3570,20 @@
       <c r="M2" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -737,9 +3633,24 @@
         <f>H3-K3</f>
         <v>1353.0900000000001</v>
       </c>
-      <c r="O3" s="5"/>
+      <c r="N3" s="8">
+        <f>VLOOKUP(M3,IRRF!$B$3:$D$7,3)</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="5">
+        <f>VLOOKUP(M3,IRRF!$B$3:$D$7,2)</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="5">
+        <f>M3*N3-O3</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="5">
+        <f>M3-P3</f>
+        <v>1353.0900000000001</v>
+      </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -789,9 +3700,24 @@
         <f t="shared" ref="M4:M20" si="4">H4-K4</f>
         <v>2335.0117500000001</v>
       </c>
-      <c r="O4" s="7"/>
+      <c r="N4" s="8">
+        <f>VLOOKUP(M4,IRRF!$B$3:$D$7,3)</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="O4" s="5">
+        <f>VLOOKUP(M4,IRRF!$B$3:$D$7,2)</f>
+        <v>169.44</v>
+      </c>
+      <c r="P4" s="5">
+        <f t="shared" ref="P4:P20" si="5">M4*N4-O4</f>
+        <v>5.6858812499999942</v>
+      </c>
+      <c r="Q4" s="5">
+        <f t="shared" ref="Q4:Q20" si="6">M4-P4</f>
+        <v>2329.3258687500002</v>
+      </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -841,9 +3767,24 @@
         <f t="shared" si="4"/>
         <v>2165.4787500000002</v>
       </c>
-      <c r="O5" s="5"/>
+      <c r="N5" s="8">
+        <f>VLOOKUP(M5,IRRF!$B$3:$D$7,3)</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="5">
+        <f>VLOOKUP(M5,IRRF!$B$3:$D$7,2)</f>
+        <v>0</v>
+      </c>
+      <c r="P5" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="5">
+        <f t="shared" si="6"/>
+        <v>2165.4787500000002</v>
+      </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -893,9 +3834,24 @@
         <f t="shared" si="4"/>
         <v>1686.7049999999999</v>
       </c>
-      <c r="O6" s="5"/>
+      <c r="N6" s="8">
+        <f>VLOOKUP(M6,IRRF!$B$3:$D$7,3)</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="5">
+        <f>VLOOKUP(M6,IRRF!$B$3:$D$7,2)</f>
+        <v>0</v>
+      </c>
+      <c r="P6" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5">
+        <f t="shared" si="6"/>
+        <v>1686.7049999999999</v>
+      </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -945,8 +3901,24 @@
         <f t="shared" si="4"/>
         <v>9674.3811999999998</v>
       </c>
+      <c r="N7" s="8">
+        <f>VLOOKUP(M7,IRRF!$B$3:$D$7,3)</f>
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="O7" s="5">
+        <f>VLOOKUP(M7,IRRF!$B$3:$D$7,2)</f>
+        <v>896</v>
+      </c>
+      <c r="P7" s="5">
+        <f t="shared" si="5"/>
+        <v>1764.4548300000001</v>
+      </c>
+      <c r="Q7" s="5">
+        <f t="shared" si="6"/>
+        <v>7909.9263699999992</v>
+      </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -996,8 +3968,24 @@
         <f t="shared" si="4"/>
         <v>4373.8899999999994</v>
       </c>
+      <c r="N8" s="8">
+        <f>VLOOKUP(M8,IRRF!$B$3:$D$7,3)</f>
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="O8" s="5">
+        <f>VLOOKUP(M8,IRRF!$B$3:$D$7,2)</f>
+        <v>662.77</v>
+      </c>
+      <c r="P8" s="5">
+        <f t="shared" si="5"/>
+        <v>321.35524999999996</v>
+      </c>
+      <c r="Q8" s="5">
+        <f t="shared" si="6"/>
+        <v>4052.5347499999993</v>
+      </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1047,8 +4035,24 @@
         <f t="shared" si="4"/>
         <v>772.28250000000003</v>
       </c>
+      <c r="N9" s="8">
+        <f>VLOOKUP(M9,IRRF!$B$3:$D$7,3)</f>
+        <v>0</v>
+      </c>
+      <c r="O9" s="5">
+        <f>VLOOKUP(M9,IRRF!$B$3:$D$7,2)</f>
+        <v>0</v>
+      </c>
+      <c r="P9" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="5">
+        <f t="shared" si="6"/>
+        <v>772.28250000000003</v>
+      </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1098,8 +4102,24 @@
         <f t="shared" si="4"/>
         <v>6717.82</v>
       </c>
+      <c r="N10" s="8">
+        <f>VLOOKUP(M10,IRRF!$B$3:$D$7,3)</f>
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="O10" s="5">
+        <f>VLOOKUP(M10,IRRF!$B$3:$D$7,2)</f>
+        <v>896</v>
+      </c>
+      <c r="P10" s="5">
+        <f t="shared" si="5"/>
+        <v>951.40049999999997</v>
+      </c>
+      <c r="Q10" s="5">
+        <f t="shared" si="6"/>
+        <v>5766.4195</v>
+      </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1149,8 +4169,24 @@
         <f t="shared" si="4"/>
         <v>2997.0720000000001</v>
       </c>
+      <c r="N11" s="8">
+        <f>VLOOKUP(M11,IRRF!$B$3:$D$7,3)</f>
+        <v>0.15</v>
+      </c>
+      <c r="O11" s="5">
+        <f>VLOOKUP(M11,IRRF!$B$3:$D$7,2)</f>
+        <v>381.44</v>
+      </c>
+      <c r="P11" s="5">
+        <f t="shared" si="5"/>
+        <v>68.120800000000031</v>
+      </c>
+      <c r="Q11" s="5">
+        <f t="shared" si="6"/>
+        <v>2928.9512</v>
+      </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1200,8 +4236,24 @@
         <f t="shared" si="4"/>
         <v>2349.1394999999998</v>
       </c>
+      <c r="N12" s="8">
+        <f>VLOOKUP(M12,IRRF!$B$3:$D$7,3)</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="O12" s="5">
+        <f>VLOOKUP(M12,IRRF!$B$3:$D$7,2)</f>
+        <v>169.44</v>
+      </c>
+      <c r="P12" s="5">
+        <f t="shared" si="5"/>
+        <v>6.7454624999999737</v>
+      </c>
+      <c r="Q12" s="5">
+        <f t="shared" si="6"/>
+        <v>2342.3940374999997</v>
+      </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1251,8 +4303,24 @@
         <f t="shared" si="4"/>
         <v>2778.48</v>
       </c>
+      <c r="N13" s="8">
+        <f>VLOOKUP(M13,IRRF!$B$3:$D$7,3)</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="O13" s="5">
+        <f>VLOOKUP(M13,IRRF!$B$3:$D$7,2)</f>
+        <v>169.44</v>
+      </c>
+      <c r="P13" s="5">
+        <f t="shared" si="5"/>
+        <v>38.945999999999998</v>
+      </c>
+      <c r="Q13" s="5">
+        <f t="shared" si="6"/>
+        <v>2739.5340000000001</v>
+      </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1302,8 +4370,24 @@
         <f t="shared" si="4"/>
         <v>3288.5279999999998</v>
       </c>
+      <c r="N14" s="8">
+        <f>VLOOKUP(M14,IRRF!$B$3:$D$7,3)</f>
+        <v>0.15</v>
+      </c>
+      <c r="O14" s="5">
+        <f>VLOOKUP(M14,IRRF!$B$3:$D$7,2)</f>
+        <v>381.44</v>
+      </c>
+      <c r="P14" s="5">
+        <f t="shared" si="5"/>
+        <v>111.83919999999995</v>
+      </c>
+      <c r="Q14" s="5">
+        <f t="shared" si="6"/>
+        <v>3176.6887999999999</v>
+      </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1353,8 +4437,24 @@
         <f t="shared" si="4"/>
         <v>3215.6640000000002</v>
       </c>
+      <c r="N15" s="8">
+        <f>VLOOKUP(M15,IRRF!$B$3:$D$7,3)</f>
+        <v>0.15</v>
+      </c>
+      <c r="O15" s="5">
+        <f>VLOOKUP(M15,IRRF!$B$3:$D$7,2)</f>
+        <v>381.44</v>
+      </c>
+      <c r="P15" s="5">
+        <f t="shared" si="5"/>
+        <v>100.90960000000001</v>
+      </c>
+      <c r="Q15" s="5">
+        <f t="shared" si="6"/>
+        <v>3114.7544000000003</v>
+      </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1404,8 +4504,24 @@
         <f t="shared" si="4"/>
         <v>1686.7049999999999</v>
       </c>
+      <c r="N16" s="8">
+        <f>VLOOKUP(M16,IRRF!$B$3:$D$7,3)</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="5">
+        <f>VLOOKUP(M16,IRRF!$B$3:$D$7,2)</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="5">
+        <f t="shared" si="6"/>
+        <v>1686.7049999999999</v>
+      </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1455,8 +4571,24 @@
         <f t="shared" si="4"/>
         <v>1611.357</v>
       </c>
+      <c r="N17" s="8">
+        <f>VLOOKUP(M17,IRRF!$B$3:$D$7,3)</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="5">
+        <f>VLOOKUP(M17,IRRF!$B$3:$D$7,2)</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="5">
+        <f t="shared" si="6"/>
+        <v>1611.357</v>
+      </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1506,8 +4638,24 @@
         <f t="shared" si="4"/>
         <v>1451.2425000000001</v>
       </c>
+      <c r="N18" s="8">
+        <f>VLOOKUP(M18,IRRF!$B$3:$D$7,3)</f>
+        <v>0</v>
+      </c>
+      <c r="O18" s="5">
+        <f>VLOOKUP(M18,IRRF!$B$3:$D$7,2)</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5">
+        <f t="shared" si="6"/>
+        <v>1451.2425000000001</v>
+      </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1557,8 +4705,24 @@
         <f t="shared" si="4"/>
         <v>2179.6064999999999</v>
       </c>
+      <c r="N19" s="8">
+        <f>VLOOKUP(M19,IRRF!$B$3:$D$7,3)</f>
+        <v>0</v>
+      </c>
+      <c r="O19" s="5">
+        <f>VLOOKUP(M19,IRRF!$B$3:$D$7,2)</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5">
+        <f t="shared" si="6"/>
+        <v>2179.6064999999999</v>
+      </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1608,8 +4772,223 @@
         <f t="shared" si="4"/>
         <v>2221.9897499999997</v>
       </c>
+      <c r="N20" s="8">
+        <f>VLOOKUP(M20,IRRF!$B$3:$D$7,3)</f>
+        <v>0</v>
+      </c>
+      <c r="O20" s="5">
+        <f>VLOOKUP(M20,IRRF!$B$3:$D$7,2)</f>
+        <v>0</v>
+      </c>
+      <c r="P20" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="5">
+        <f t="shared" si="6"/>
+        <v>2221.9897499999997</v>
+      </c>
+      <c r="R20" t="s">
+        <v>63</v>
+      </c>
+      <c r="S20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="5">
+        <f>SUM(C3:C20)</f>
+        <v>54344.4</v>
+      </c>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5">
+        <f t="shared" ref="D21:Q21" si="7">SUM(G3:G20)</f>
+        <v>3713.9250000000002</v>
+      </c>
+      <c r="H21" s="5">
+        <f t="shared" si="7"/>
+        <v>58058.324999999997</v>
+      </c>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5">
+        <f t="shared" si="7"/>
+        <v>5199.8815499999992</v>
+      </c>
+      <c r="L21" s="5">
+        <f t="shared" si="7"/>
+        <v>4644.6660000000011</v>
+      </c>
+      <c r="M21" s="5">
+        <f t="shared" si="7"/>
+        <v>52858.443449999999</v>
+      </c>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5">
+        <f t="shared" si="7"/>
+        <v>3369.4575237500003</v>
+      </c>
+      <c r="Q21" s="5">
+        <f t="shared" si="7"/>
+        <v>49488.985926250003</v>
+      </c>
+      <c r="R21" s="5">
+        <f>H21+L21+(H21+L21)*22%</f>
+        <v>76497.649019999997</v>
+      </c>
+      <c r="S21" s="5">
+        <f>R21*5%</f>
+        <v>3824.8824509999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" s="12"/>
+      <c r="B22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="5">
+        <f>AVERAGE(C3:C20)</f>
+        <v>3019.1333333333332</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5">
+        <f t="shared" ref="D22:Q22" si="8">AVERAGE(G3:G20)</f>
+        <v>206.32916666666668</v>
+      </c>
+      <c r="H22" s="5">
+        <f t="shared" si="8"/>
+        <v>3225.4624999999996</v>
+      </c>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5">
+        <f t="shared" si="8"/>
+        <v>288.8823083333333</v>
+      </c>
+      <c r="L22" s="5">
+        <f t="shared" si="8"/>
+        <v>258.03700000000003</v>
+      </c>
+      <c r="M22" s="5">
+        <f t="shared" si="8"/>
+        <v>2936.5801916666665</v>
+      </c>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5">
+        <f t="shared" si="8"/>
+        <v>187.19208465277779</v>
+      </c>
+      <c r="Q22" s="5">
+        <f t="shared" si="8"/>
+        <v>2749.3881070138891</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" s="12"/>
+      <c r="B23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="5">
+        <f>MAX(C3:C20)</f>
+        <v>10626</v>
+      </c>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5">
+        <f t="shared" ref="D23:Q23" si="9">MAX(G3:G20)</f>
+        <v>579.6</v>
+      </c>
+      <c r="H23" s="5">
+        <f t="shared" si="9"/>
+        <v>10626</v>
+      </c>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5">
+        <f t="shared" si="9"/>
+        <v>951.61880000000008</v>
+      </c>
+      <c r="L23" s="5">
+        <f t="shared" si="9"/>
+        <v>850.08</v>
+      </c>
+      <c r="M23" s="5">
+        <f t="shared" si="9"/>
+        <v>9674.3811999999998</v>
+      </c>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5">
+        <f t="shared" si="9"/>
+        <v>1764.4548300000001</v>
+      </c>
+      <c r="Q23" s="5">
+        <f t="shared" si="9"/>
+        <v>7909.9263699999992</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="12"/>
+      <c r="B24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="5">
+        <f>MIN(C3:C20)</f>
+        <v>759</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5">
+        <f t="shared" ref="D24:Q24" si="10">MIN(G3:G20)</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="5">
+        <f t="shared" si="10"/>
+        <v>834.9</v>
+      </c>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5">
+        <f t="shared" si="10"/>
+        <v>62.617499999999993</v>
+      </c>
+      <c r="L24" s="5">
+        <f t="shared" si="10"/>
+        <v>66.792000000000002</v>
+      </c>
+      <c r="M24" s="5">
+        <f t="shared" si="10"/>
+        <v>772.28250000000003</v>
+      </c>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="5">
+        <f t="shared" si="10"/>
+        <v>772.28250000000003</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A21:A24"/>
+  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -1626,44 +5005,49 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C85C68A-4D81-4AAD-8B7A-2E5F7F612CAE}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -1671,17 +5055,21 @@
         <v>0.8</v>
       </c>
       <c r="C3" s="2">
-        <f>B3*$F$3</f>
+        <f>B3*$G$3</f>
         <v>1214.4000000000001</v>
       </c>
       <c r="D3">
         <v>110</v>
       </c>
-      <c r="F3" s="2">
+      <c r="E3">
+        <f>SUMIF(Pagamentos!$B$3:$B$20,Cargos!A3,Pagamentos!$F$3:$F$20)</f>
+        <v>15</v>
+      </c>
+      <c r="G3" s="2">
         <v>1518</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -1689,14 +5077,18 @@
         <v>1.5</v>
       </c>
       <c r="C4" s="2">
-        <f t="shared" ref="C4:C13" si="0">B4*$F$3</f>
+        <f t="shared" ref="C4:C13" si="0">B4*$G$3</f>
         <v>2277</v>
       </c>
       <c r="D4">
         <v>220</v>
       </c>
+      <c r="E4">
+        <f>SUMIF(Pagamentos!$B$3:$B$20,Cargos!A4,Pagamentos!$F$3:$F$20)</f>
+        <v>26</v>
+      </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -1710,8 +5102,12 @@
       <c r="D5">
         <v>220</v>
       </c>
+      <c r="E5">
+        <f>SUMIF(Pagamentos!$B$3:$B$20,Cargos!A5,Pagamentos!$F$3:$F$20)</f>
+        <v>11</v>
+      </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -1725,8 +5121,12 @@
       <c r="D6">
         <v>220</v>
       </c>
+      <c r="E6">
+        <f>SUMIF(Pagamentos!$B$3:$B$20,Cargos!A6,Pagamentos!$F$3:$F$20)</f>
+        <v>87</v>
+      </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -1740,8 +5140,12 @@
       <c r="D7">
         <v>220</v>
       </c>
+      <c r="E7">
+        <f>SUMIF(Pagamentos!$B$3:$B$20,Cargos!A7,Pagamentos!$F$3:$F$20)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -1755,8 +5159,12 @@
       <c r="D8">
         <v>220</v>
       </c>
+      <c r="E8">
+        <f>SUMIF(Pagamentos!$B$3:$B$20,Cargos!A8,Pagamentos!$F$3:$F$20)</f>
+        <v>10</v>
+      </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -1770,8 +5178,12 @@
       <c r="D9">
         <v>180</v>
       </c>
+      <c r="E9">
+        <f>SUMIF(Pagamentos!$B$3:$B$20,Cargos!A9,Pagamentos!$F$3:$F$20)</f>
+        <v>12</v>
+      </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -1785,8 +5197,12 @@
       <c r="D10">
         <v>220</v>
       </c>
+      <c r="E10">
+        <f>SUMIF(Pagamentos!$B$3:$B$20,Cargos!A10,Pagamentos!$F$3:$F$20)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -1800,8 +5216,12 @@
       <c r="D11">
         <v>220</v>
       </c>
+      <c r="E11">
+        <f>SUMIF(Pagamentos!$B$3:$B$20,Cargos!A11,Pagamentos!$F$3:$F$20)</f>
+        <v>64</v>
+      </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -1815,8 +5235,12 @@
       <c r="D12">
         <v>220</v>
       </c>
+      <c r="E12">
+        <f>SUMIF(Pagamentos!$B$3:$B$20,Cargos!A12,Pagamentos!$F$3:$F$20)</f>
+        <v>18</v>
+      </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -1829,6 +5253,10 @@
       </c>
       <c r="D13">
         <v>220</v>
+      </c>
+      <c r="E13">
+        <f>SUMIF(Pagamentos!$B$3:$B$20,Cargos!A13,Pagamentos!$F$3:$F$20)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1836,13 +5264,14 @@
     <sortCondition ref="A2:A12"/>
   </sortState>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE3E2113-A20F-4752-9D6B-FCDAD72F6143}">
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1855,11 +5284,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -1961,7 +5390,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{634D263C-688C-4774-B4A2-E57A21E8F14C}">
   <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1973,11 +5402,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -2014,7 +5443,7 @@
       <c r="C4" s="2">
         <v>169.44</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="9">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="F4" s="2"/>
@@ -2029,7 +5458,7 @@
       <c r="C5" s="2">
         <v>381.44</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="9">
         <v>0.15</v>
       </c>
       <c r="I5" s="5"/>
@@ -2044,7 +5473,7 @@
       <c r="C6" s="2">
         <v>662.77</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="9">
         <v>0.22500000000000001</v>
       </c>
       <c r="I6" s="5"/>
@@ -2059,7 +5488,7 @@
       <c r="C7" s="2">
         <v>896</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="9">
         <v>0.27500000000000002</v>
       </c>
       <c r="F7" s="5"/>
